--- a/data/industry/CFM/OEM SSD.xlsx
+++ b/data/industry/CFM/OEM SSD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94AF2EEC-F6E5-43D8-AAFD-695227F0AFA3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8E4438-F3FA-491A-B271-9CB8E15CE9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OEM SSD 256GB SATA" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -457,15 +457,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -1226,6 +1226,144 @@
       </c>
       <c r="G33" s="12">
         <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>59</v>
+      </c>
+      <c r="F34" s="12">
+        <v>63</v>
+      </c>
+      <c r="G34" s="12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>59</v>
+      </c>
+      <c r="F35" s="12">
+        <v>63</v>
+      </c>
+      <c r="G35" s="12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>59</v>
+      </c>
+      <c r="F36" s="12">
+        <v>63</v>
+      </c>
+      <c r="G36" s="12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>59</v>
+      </c>
+      <c r="F37" s="12">
+        <v>63</v>
+      </c>
+      <c r="G37" s="12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>59</v>
+      </c>
+      <c r="F38" s="12">
+        <v>63</v>
+      </c>
+      <c r="G38" s="12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>59</v>
+      </c>
+      <c r="F39" s="12">
+        <v>63</v>
+      </c>
+      <c r="G39" s="12">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1236,15 +1374,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F473D36E-208F-4614-83B5-69AB6F33294E}">
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -2005,6 +2143,144 @@
       </c>
       <c r="G33" s="12">
         <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>110</v>
+      </c>
+      <c r="F34" s="12">
+        <v>117</v>
+      </c>
+      <c r="G34" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>110</v>
+      </c>
+      <c r="F35" s="12">
+        <v>117</v>
+      </c>
+      <c r="G35" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>110</v>
+      </c>
+      <c r="F36" s="12">
+        <v>117</v>
+      </c>
+      <c r="G36" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>110</v>
+      </c>
+      <c r="F37" s="12">
+        <v>117</v>
+      </c>
+      <c r="G37" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>110</v>
+      </c>
+      <c r="F38" s="12">
+        <v>117</v>
+      </c>
+      <c r="G38" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>110</v>
+      </c>
+      <c r="F39" s="12">
+        <v>117</v>
+      </c>
+      <c r="G39" s="12">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -2015,15 +2291,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6C0178-E414-47B2-A630-84DA7232A61F}">
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -2783,6 +3059,144 @@
         <v>192</v>
       </c>
       <c r="G33" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>188</v>
+      </c>
+      <c r="F34" s="12">
+        <v>192</v>
+      </c>
+      <c r="G34" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>188</v>
+      </c>
+      <c r="F35" s="12">
+        <v>192</v>
+      </c>
+      <c r="G35" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>188</v>
+      </c>
+      <c r="F36" s="12">
+        <v>192</v>
+      </c>
+      <c r="G36" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>188</v>
+      </c>
+      <c r="F37" s="12">
+        <v>192</v>
+      </c>
+      <c r="G37" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>188</v>
+      </c>
+      <c r="F38" s="12">
+        <v>192</v>
+      </c>
+      <c r="G38" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>188</v>
+      </c>
+      <c r="F39" s="12">
+        <v>192</v>
+      </c>
+      <c r="G39" s="12">
         <v>190</v>
       </c>
     </row>
@@ -2794,15 +3208,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE21688-DF7E-4F8C-887E-342649A09FB0}">
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -3563,6 +3977,144 @@
       </c>
       <c r="G33" s="12">
         <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>60.5</v>
+      </c>
+      <c r="F34" s="12">
+        <v>63</v>
+      </c>
+      <c r="G34" s="12">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>60.5</v>
+      </c>
+      <c r="F35" s="12">
+        <v>63</v>
+      </c>
+      <c r="G35" s="12">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>60.5</v>
+      </c>
+      <c r="F36" s="12">
+        <v>63</v>
+      </c>
+      <c r="G36" s="12">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>60.5</v>
+      </c>
+      <c r="F37" s="12">
+        <v>63</v>
+      </c>
+      <c r="G37" s="12">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>60.5</v>
+      </c>
+      <c r="F38" s="12">
+        <v>63</v>
+      </c>
+      <c r="G38" s="12">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>60.5</v>
+      </c>
+      <c r="F39" s="12">
+        <v>63</v>
+      </c>
+      <c r="G39" s="12">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -3573,15 +4125,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{075E49D7-A50C-4EF3-8D98-3E3352C23834}">
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -4342,6 +4894,144 @@
       </c>
       <c r="G33" s="12">
         <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>112.5</v>
+      </c>
+      <c r="F34" s="12">
+        <v>118</v>
+      </c>
+      <c r="G34" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>112.5</v>
+      </c>
+      <c r="F35" s="12">
+        <v>118</v>
+      </c>
+      <c r="G35" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>112.5</v>
+      </c>
+      <c r="F36" s="12">
+        <v>118</v>
+      </c>
+      <c r="G36" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>112.5</v>
+      </c>
+      <c r="F37" s="12">
+        <v>118</v>
+      </c>
+      <c r="G37" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>112.5</v>
+      </c>
+      <c r="F38" s="12">
+        <v>118</v>
+      </c>
+      <c r="G38" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>112.5</v>
+      </c>
+      <c r="F39" s="12">
+        <v>118</v>
+      </c>
+      <c r="G39" s="12">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -4352,15 +5042,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18515E64-A7B9-4EA8-8571-9A16CD6B2FD3}">
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -5120,6 +5810,144 @@
         <v>192</v>
       </c>
       <c r="G33" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>189</v>
+      </c>
+      <c r="F34" s="12">
+        <v>192</v>
+      </c>
+      <c r="G34" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>189</v>
+      </c>
+      <c r="F35" s="12">
+        <v>192</v>
+      </c>
+      <c r="G35" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>189</v>
+      </c>
+      <c r="F36" s="12">
+        <v>192</v>
+      </c>
+      <c r="G36" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>189</v>
+      </c>
+      <c r="F37" s="12">
+        <v>192</v>
+      </c>
+      <c r="G37" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>189</v>
+      </c>
+      <c r="F38" s="12">
+        <v>192</v>
+      </c>
+      <c r="G38" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>189</v>
+      </c>
+      <c r="F39" s="12">
+        <v>192</v>
+      </c>
+      <c r="G39" s="12">
         <v>190</v>
       </c>
     </row>
@@ -5131,15 +5959,15 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8286ED8B-68EC-4D79-8787-976F03BA0C32}">
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -5900,6 +6728,144 @@
       </c>
       <c r="G33" s="12">
         <v>115</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>116</v>
+      </c>
+      <c r="F34" s="12">
+        <v>120</v>
+      </c>
+      <c r="G34" s="12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>116</v>
+      </c>
+      <c r="F35" s="12">
+        <v>120</v>
+      </c>
+      <c r="G35" s="12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>116</v>
+      </c>
+      <c r="F36" s="12">
+        <v>120</v>
+      </c>
+      <c r="G36" s="12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>116</v>
+      </c>
+      <c r="F37" s="12">
+        <v>120</v>
+      </c>
+      <c r="G37" s="12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>116</v>
+      </c>
+      <c r="F38" s="12">
+        <v>120</v>
+      </c>
+      <c r="G38" s="12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>116</v>
+      </c>
+      <c r="F39" s="12">
+        <v>120</v>
+      </c>
+      <c r="G39" s="12">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -5910,15 +6876,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62752974-E8DF-439D-ACF9-ECD10A65F3F8}">
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -6678,6 +7644,144 @@
         <v>201</v>
       </c>
       <c r="G33" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="14">
+        <v>198</v>
+      </c>
+      <c r="F34" s="14">
+        <v>201</v>
+      </c>
+      <c r="G34" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="14">
+        <v>198</v>
+      </c>
+      <c r="F35" s="14">
+        <v>201</v>
+      </c>
+      <c r="G35" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="14">
+        <v>198</v>
+      </c>
+      <c r="F36" s="14">
+        <v>201</v>
+      </c>
+      <c r="G36" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="14">
+        <v>198</v>
+      </c>
+      <c r="F37" s="14">
+        <v>201</v>
+      </c>
+      <c r="G37" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="14">
+        <v>198</v>
+      </c>
+      <c r="F38" s="14">
+        <v>201</v>
+      </c>
+      <c r="G38" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="14">
+        <v>198</v>
+      </c>
+      <c r="F39" s="14">
+        <v>201</v>
+      </c>
+      <c r="G39" s="14">
         <v>200</v>
       </c>
     </row>
@@ -6689,15 +7793,15 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9F2B4-31D6-4C55-BAC0-7D448A9FC534}">
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -7460,6 +8564,144 @@
         <v>380</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="9">
+        <v>378</v>
+      </c>
+      <c r="F34" s="9">
+        <v>385</v>
+      </c>
+      <c r="G34" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="9">
+        <v>378</v>
+      </c>
+      <c r="F35" s="9">
+        <v>385</v>
+      </c>
+      <c r="G35" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="9">
+        <v>378</v>
+      </c>
+      <c r="F36" s="9">
+        <v>385</v>
+      </c>
+      <c r="G36" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="9">
+        <v>378</v>
+      </c>
+      <c r="F37" s="9">
+        <v>385</v>
+      </c>
+      <c r="G37" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="9">
+        <v>378</v>
+      </c>
+      <c r="F38" s="9">
+        <v>385</v>
+      </c>
+      <c r="G38" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="9">
+        <v>378</v>
+      </c>
+      <c r="F39" s="9">
+        <v>385</v>
+      </c>
+      <c r="G39" s="9">
+        <v>380</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
